--- a/conformance/cases/xlsx-03-title-offset.xlsx
+++ b/conformance/cases/xlsx-03-title-offset.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luồng trong Excel</t>
+          <t xml:space="preserve">Flow in Excel</t>
         </is>
       </c>
     </row>
@@ -97,7 +97,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -114,7 +114,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -141,7 +141,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xử lý</t>
+          <t xml:space="preserve">Process</t>
         </is>
       </c>
     </row>
@@ -180,7 +180,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
@@ -188,7 +188,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghi chú dưới bảng</t>
+          <t xml:space="preserve">note below table</t>
         </is>
       </c>
     </row>
